--- a/Nefunkcionalny_cheklist_Diplomnaya_rabota.xlsx
+++ b/Nefunkcionalny_cheklist_Diplomnaya_rabota.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нефункц. чек-лист" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нефункциональный чек-лист" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Итоги" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
@@ -41,25 +41,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9EAD3"/>
-        <bgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F4CCCC"/>
-        <bgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -73,16 +69,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00999999"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00999999"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00999999"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00999999"/>
       </bottom>
     </border>
   </borders>
@@ -92,7 +88,7 @@
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -478,7 +474,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -519,7 +515,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Все ключевые элементы (поиск, каталог, корзина) видны без прокрутки на десктопе (1920×1080)</t>
+          <t>Ключевые элементы (поиск, каталог, корзина) видны без прокрутки на десктопе (1920×1080)</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -529,7 +525,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Проверено визуально, масштаб 125% (1536×864 лог. px)</t>
+          <t>Проверено визуально в Chrome, масштаб Windows 125%</t>
         </is>
       </c>
     </row>
@@ -579,7 +575,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Циклически показываются примеры запросов</t>
+          <t>В плейсхолдере по очереди показываются примеры запросов</t>
         </is>
       </c>
     </row>
@@ -594,7 +590,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Изображения товаров загружаются без задержек и разрывов вёрстки</t>
+          <t>Изображения товаров загружаются без разрывов вёрстки в сетке карточек</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -604,7 +600,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Проверено визуально на сетке карточек</t>
+          <t>Проверено визуально на сетке карточек товаров. Сдвиги макета страницы в целом — см. пункт 12 (BR-002)</t>
         </is>
       </c>
     </row>
@@ -619,7 +615,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Главная страница корректно отображается в Chrome</t>
+          <t>Главная страница корректно отображается в Google Chrome</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -629,7 +625,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Основной браузер проверки, ошибок в консоли нет</t>
+          <t>Chrome, десктоп: вёрстка корректна, ошибок в консоли нет</t>
         </is>
       </c>
     </row>
@@ -644,7 +640,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Главная страница корректно отображается в Firefox</t>
+          <t>Главная страница корректно отображается в Яндекс Браузере</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -654,7 +650,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Инструменты автоматизации в сессии управляют только Chrome</t>
+          <t>Ожидает ручной проверки</t>
         </is>
       </c>
     </row>
@@ -669,7 +665,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Главная страница корректно отображается в Edge</t>
+          <t>Главная страница корректно отображается в Microsoft Edge</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -679,7 +675,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>То же ограничение инструментов</t>
+          <t>Ожидает ручной проверки</t>
         </is>
       </c>
     </row>
@@ -694,7 +690,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Основные интерактивные элементы (поиск, каталог, корзина) доступны через Tab с клавиатуры</t>
+          <t>Основные интерактивные элементы (поиск, каталог, корзина) доступны с клавиатуры клавишей Tab</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -704,7 +700,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Проверено реальным нажатием Tab, фокус подтверждён</t>
+          <t>Фокус последовательно переходит на поиск, каталог и корзину</t>
         </is>
       </c>
     </row>
@@ -719,7 +715,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Контраст текста на баннерах соответствует WCAG AA</t>
+          <t>Контраст текста на бейджах и баннерах соответствует WCAG 2.1 AA (не ниже 4,5:1)</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -729,7 +725,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Найден дефект BR-001 (бейдж скидки, контраст 4.04:1 при пороге 4.5:1)</t>
+          <t>Дефект BR-001: бейдж скидки, контраст 4,04:1</t>
         </is>
       </c>
     </row>
@@ -744,7 +740,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>У изображений товаров есть атрибуты alt для скринридеров</t>
+          <t>У изображений товаров есть атрибут alt для экранных чтецов</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -754,7 +750,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40 из 40 проверенных img имеют непустой alt</t>
+          <t>27 из 27 изображений товаров на главной странице имеют непустой alt</t>
         </is>
       </c>
     </row>
@@ -769,7 +765,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Largest Contentful Paint (LCP) в диапазоне «хорошо» (≤2.5 сек)</t>
+          <t>Largest Contentful Paint (LCP) в диапазоне «хорошо» (не больше 2,5 сек)</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -779,7 +775,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>LCP = 2 сек. Реальные данные пользователей Chrome (CrUX) за 28 дней, pagespeed.web.dev, 23.09.2026</t>
+          <t>LCP = 2 сек, данные пользователей Chrome за 28 дней, PageSpeed Insights, компьютеры</t>
         </is>
       </c>
     </row>
@@ -794,7 +790,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Cumulative Layout Shift (CLS) в диапазоне «хорошо» (≤0.1)</t>
+          <t>Cumulative Layout Shift (CLS) в диапазоне «хорошо» (не больше 0,1)</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -804,7 +800,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Найден дефект BR-002: CLS = 0.7 (диапазон «плохо», порог «плохо» &gt;0.25). pagespeed.web.dev, реальные данные пользователей, 23.09.2026</t>
+          <t>Дефект BR-002: CLS = 0,7 (диапазон «плохо»), PageSpeed Insights, компьютеры</t>
         </is>
       </c>
     </row>
@@ -823,7 +819,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -871,7 +867,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Не проверено (ограничение инструментов)</t>
+          <t>Не проверено</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -898,7 +894,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>BR-001 (контраст, Low), BR-002 (CLS, Medium)</t>
+          <t>BR-001 (контраст бейджа скидки: серьёзность Minor, приоритет Low); BR-002 (сдвиги макета, CLS 0,7: серьёзность Major, приоритет Medium)</t>
         </is>
       </c>
     </row>

--- a/Nefunkcionalny_cheklist_Diplomnaya_rabota.xlsx
+++ b/Nefunkcionalny_cheklist_Diplomnaya_rabota.xlsx
@@ -31,7 +31,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -46,11 +46,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9EAD3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -85,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -97,9 +92,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -643,14 +635,14 @@
           <t>Главная страница корректно отображается в Яндекс Браузере</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>НЕ ПРОВЕРЕНО</t>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>ПРОЙДЕНО</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Ожидает ручной проверки</t>
+          <t>Проверено вручную 23.09.2026: главная страница отображается корректно</t>
         </is>
       </c>
     </row>
@@ -668,14 +660,14 @@
           <t>Главная страница корректно отображается в Microsoft Edge</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>НЕ ПРОВЕРЕНО</t>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>ПРОЙДЕНО</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Ожидает ручной проверки</t>
+          <t>Проверено вручную 23.09.2026: главная страница отображается корректно</t>
         </is>
       </c>
     </row>
@@ -718,7 +710,7 @@
           <t>Контраст текста на бейджах и баннерах соответствует WCAG 2.1 AA (не ниже 4,5:1)</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>НЕ ПРОЙДЕНО</t>
         </is>
@@ -793,7 +785,7 @@
           <t>Cumulative Layout Shift (CLS) в диапазоне «хорошо» (не больше 0,1)</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>НЕ ПРОЙДЕНО</t>
         </is>
@@ -815,7 +807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -851,7 +843,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -867,44 +859,34 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>2</v>
+          <t>Виды тестирования</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>UI/UX, кросс-браузерность, доступность, производительность</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Виды тестирования</t>
+          <t>Найденные дефекты</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>UI/UX, кросс-браузерность, доступность, производительность</t>
+          <t>BR-001 (контраст бейджа скидки: серьёзность Minor, приоритет Low); BR-002 (сдвиги макета, CLS 0,7: серьёзность Major, приоритет Medium)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Найденные дефекты</t>
+          <t>Дата прогона</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>BR-001 (контраст бейджа скидки: серьёзность Minor, приоритет Low); BR-002 (сдвиги макета, CLS 0,7: серьёзность Major, приоритет Medium)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Дата прогона</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>23.09.2026</t>
         </is>

--- a/Nefunkcionalny_cheklist_Diplomnaya_rabota.xlsx
+++ b/Nefunkcionalny_cheklist_Diplomnaya_rabota.xlsx
@@ -642,7 +642,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Проверено вручную 23.09.2026: главная страница отображается корректно</t>
+          <t>Проверено вручную: вёрстка главной не ломается, шапка с поиском, каталог, корзина и сетка карточек товаров на месте, кнопки и шрифты отображаются</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Проверено вручную 23.09.2026: главная страница отображается корректно</t>
+          <t>Проверено вручную: вёрстка главной не ломается, шапка с поиском, каталог, корзина и сетка карточек товаров на месте, кнопки и шрифты отображаются</t>
         </is>
       </c>
     </row>
@@ -807,7 +807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -871,7 +871,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Найденные дефекты</t>
+          <t>Дефекты по чек-листу</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -883,10 +883,22 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>Дефект API</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>BR-003 (500 на несуществующий customerCityId: серьёзность Major, приоритет Medium) — см. тест-кейс TC-API-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
           <t>Дата прогона</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>23.09.2026</t>
         </is>
